--- a/Result/profitability/1467.xlsx
+++ b/Result/profitability/1467.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02874999999999997</v>
+        <v>-0.08874999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>18.915</v>
+        <v>18.37</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.09249999999999997</v>
+        <v>-0.12625</v>
       </c>
       <c r="N3" t="n">
-        <v>17.815</v>
+        <v>17.5075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03874999999999998</v>
+        <v>-0.06624999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>16.97</v>
+        <v>16.9425</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.17125</v>
+        <v>-0.09249999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>15.7175</v>
+        <v>15.81125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03499999999999999</v>
+        <v>-0.06124999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>15.77</v>
+        <v>15.775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01999999999999999</v>
+        <v>-0.08749999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>15.74</v>
+        <v>15.0625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06749999999999999</v>
+        <v>-0.10625</v>
       </c>
       <c r="N8" t="n">
-        <v>14.57625</v>
+        <v>14.3525</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.15</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06249999999999999</v>
+        <v>-0.06249999999999997</v>
       </c>
       <c r="N9" t="n">
         <v>14.24625</v>
@@ -1645,7 +1645,7 @@
         <v>0.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000002</v>
       </c>
       <c r="N10" t="n">
         <v>15.3325</v>
@@ -1772,7 +1772,7 @@
         <v>-0.11</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02500000000000001</v>
+        <v>0.02500000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>14.99</v>
@@ -1899,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.08750000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>15.63</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1279</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1049</v>
+      </c>
+      <c r="E75" t="n">
+        <v>230</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.02499999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.6525</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.818181818181818</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.790000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09058704453441313</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7590361445783133</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04355400696864109</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
